--- a/uorgs.xlsx
+++ b/uorgs.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CC935F2-78B7-4787-915E-0EA50D539B21}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD118E11-12A7-4DF6-9AC8-1B2F238BD35E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{EA73E3BE-6EDE-450B-BDC6-32103B9FB15B}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista de UORGs e Departamen (2)" sheetId="3" r:id="rId1"/>
-    <sheet name="Lista de UORGs e Departamentos" sheetId="1" r:id="rId2"/>
-    <sheet name="Lista de UORGs" sheetId="2" r:id="rId3"/>
+    <sheet name="UORGs" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de UORGs e Departamen (2)'!$A$2:$E$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Lista de UORGs e Departamentos'!$A$2:$C$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$299</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="335">
   <si>
     <t>ACP-SAR</t>
   </si>
@@ -1559,10 +1558,10 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1959,26 +1958,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>321</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -7226,3598 +7225,2466 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}">
-  <dimension ref="A1:F300"/>
+  <dimension ref="A1:E299"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.26953125" customWidth="1"/>
     <col min="2" max="2" width="20.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="29.54296875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.26953125" customWidth="1"/>
-    <col min="5" max="5" width="16.08984375" customWidth="1"/>
-    <col min="6" max="6" width="11.6328125" customWidth="1"/>
+    <col min="3" max="3" width="21.26953125" customWidth="1"/>
+    <col min="4" max="4" width="16.08984375" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>321</v>
-      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>332</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="D7" s="1"/>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="D8" s="2"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="D10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>18</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="D11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>18</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>18</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>20</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="D15" s="2"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D20" s="2"/>
       <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="1"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="D23" s="2"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>7</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>26</v>
+        <v>333</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>333</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>333</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>334</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>334</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>334</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>334</v>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
-        <v>331</v>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>143</v>
+        <v>330</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>329</v>
+        <v>300</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>326</v>
+        <v>301</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>308</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>308</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>308</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>308</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>308</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>308</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>308</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>308</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.35">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.35">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.35">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.35">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.35">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.35">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.35">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.35">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.35">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.35">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.35">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>310</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C211" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.35">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C213" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.35">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.35">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.35">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.35">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.35">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.35">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>313</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.35">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.35">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.35">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.35">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.35">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.35">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.35">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.35">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.35">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.35">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.35">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.35">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.35">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.35">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.35">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.35">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.35">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.35">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.35">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.35">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C287" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.35">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.35">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.35">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>316</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.35">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>318</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.35">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>318</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>318</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>318</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.35">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>318</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.35">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>318</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A300" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B300" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C300" s="2" t="s">
-        <v>67</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C300" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C300">
-    <sortCondition ref="A3:A300"/>
+  <autoFilter ref="A1:B299" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B299">
+    <sortCondition ref="A2:A299"/>
   </sortState>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C34" r:id="rId1" xr:uid="{C8A760F7-C7A1-4AA3-B682-C0CC1EA542F0}"/>
-    <hyperlink ref="C45" r:id="rId2" xr:uid="{2C5BA511-7986-4098-97A8-8B5312B9B652}"/>
-  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75FAE0D0-6912-4EE6-9F1C-CE984D17118E}">
-  <dimension ref="D1:E26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="4" width="18.453125" customWidth="1"/>
-    <col min="5" max="5" width="19.26953125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D1" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="2" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D2" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D10" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D11" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E11" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D12" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D13" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D14" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E14" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="4:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="D15" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E15" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D16" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E16" s="1">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D17" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E17" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D18" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E18" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D19" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E19" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D20" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E20" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D21" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="E21" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D22" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E22" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D23" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E23" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D24" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E24" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D25" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E25" s="1">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="4:5" x14ac:dyDescent="0.35">
-      <c r="D26" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E26" s="1">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/uorgs.xlsx
+++ b/uorgs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD118E11-12A7-4DF6-9AC8-1B2F238BD35E}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F00C01C-CFE8-40A2-A424-A20E410ADF94}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{EA73E3BE-6EDE-450B-BDC6-32103B9FB15B}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de UORGs e Departamen (2)'!$A$2:$E$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$299</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$302</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="338">
   <si>
     <t>ACP-SAR</t>
   </si>
@@ -1043,13 +1043,22 @@
   </si>
   <si>
     <t>CORREGEDORIA</t>
+  </si>
+  <si>
+    <t>CAAS</t>
+  </si>
+  <si>
+    <t>CCAV</t>
+  </si>
+  <si>
+    <t>CGRV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1191,6 +1200,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="35">
@@ -1547,7 +1562,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1562,6 +1577,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7225,7 +7243,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}">
-  <dimension ref="A1:E299"/>
+  <dimension ref="A1:E302"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.26953125" customWidth="1"/>
@@ -8651,24 +8669,24 @@
       <c r="A171" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B171" s="2" t="s">
-        <v>62</v>
+      <c r="B171" s="6" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B172" s="2" t="s">
-        <v>86</v>
+      <c r="B172" s="6" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B173" s="2" t="s">
-        <v>87</v>
+      <c r="B173" s="6" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
@@ -8676,7 +8694,7 @@
         <v>310</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
@@ -8684,7 +8702,7 @@
         <v>310</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -8692,7 +8710,7 @@
         <v>310</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -8700,7 +8718,7 @@
         <v>310</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
@@ -8708,7 +8726,7 @@
         <v>310</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
@@ -8716,7 +8734,7 @@
         <v>310</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
@@ -8724,7 +8742,7 @@
         <v>310</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
@@ -8732,7 +8750,7 @@
         <v>310</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -8740,7 +8758,7 @@
         <v>310</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
@@ -8748,7 +8766,7 @@
         <v>310</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
@@ -8756,7 +8774,7 @@
         <v>310</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -8764,7 +8782,7 @@
         <v>310</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -8772,7 +8790,7 @@
         <v>310</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -8780,7 +8798,7 @@
         <v>310</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -8788,7 +8806,7 @@
         <v>310</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>200</v>
+        <v>172</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -8796,7 +8814,7 @@
         <v>310</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -8804,7 +8822,7 @@
         <v>310</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -8812,7 +8830,7 @@
         <v>310</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -8820,7 +8838,7 @@
         <v>310</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -8828,7 +8846,7 @@
         <v>310</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -8836,7 +8854,7 @@
         <v>310</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
@@ -8844,7 +8862,7 @@
         <v>310</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -8852,7 +8870,7 @@
         <v>310</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -8860,7 +8878,7 @@
         <v>310</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>279</v>
+        <v>229</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -8868,7 +8886,7 @@
         <v>310</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -8876,7 +8894,7 @@
         <v>310</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>288</v>
+        <v>236</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -8884,7 +8902,7 @@
         <v>310</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -8892,31 +8910,31 @@
         <v>310</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>320</v>
+        <v>287</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>29</v>
+        <v>288</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>37</v>
+        <v>310</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>40</v>
+        <v>320</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
@@ -8924,7 +8942,7 @@
         <v>313</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
@@ -8932,7 +8950,7 @@
         <v>313</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
@@ -8940,7 +8958,7 @@
         <v>313</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -8948,7 +8966,7 @@
         <v>313</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
@@ -8956,7 +8974,7 @@
         <v>313</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
@@ -8964,7 +8982,7 @@
         <v>313</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -8972,7 +8990,7 @@
         <v>313</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -8980,7 +8998,7 @@
         <v>313</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
@@ -8988,7 +9006,7 @@
         <v>313</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
@@ -8996,7 +9014,7 @@
         <v>313</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
@@ -9004,7 +9022,7 @@
         <v>313</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
@@ -9012,7 +9030,7 @@
         <v>313</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
@@ -9020,7 +9038,7 @@
         <v>313</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -9028,7 +9046,7 @@
         <v>313</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -9036,7 +9054,7 @@
         <v>313</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
@@ -9044,7 +9062,7 @@
         <v>313</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -9052,7 +9070,7 @@
         <v>313</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -9060,7 +9078,7 @@
         <v>313</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
@@ -9068,7 +9086,7 @@
         <v>313</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
@@ -9076,7 +9094,7 @@
         <v>313</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -9084,7 +9102,7 @@
         <v>313</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
@@ -9092,7 +9110,7 @@
         <v>313</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
@@ -9100,7 +9118,7 @@
         <v>313</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
@@ -9108,7 +9126,7 @@
         <v>313</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -9116,7 +9134,7 @@
         <v>313</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
@@ -9124,7 +9142,7 @@
         <v>313</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -9132,7 +9150,7 @@
         <v>313</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
@@ -9140,7 +9158,7 @@
         <v>313</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -9148,7 +9166,7 @@
         <v>313</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
@@ -9156,7 +9174,7 @@
         <v>313</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -9164,7 +9182,7 @@
         <v>313</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>230</v>
+        <v>176</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -9172,7 +9190,7 @@
         <v>313</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>241</v>
+        <v>193</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -9180,7 +9198,7 @@
         <v>313</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>303</v>
+        <v>201</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -9188,31 +9206,31 @@
         <v>313</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>313</v>
+        <v>230</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>21</v>
+        <v>241</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>44</v>
+        <v>303</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>50</v>
+        <v>313</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -9220,7 +9238,7 @@
         <v>314</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
@@ -9228,7 +9246,7 @@
         <v>314</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -9236,7 +9254,7 @@
         <v>314</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -9244,7 +9262,7 @@
         <v>314</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -9252,7 +9270,7 @@
         <v>314</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
@@ -9260,7 +9278,7 @@
         <v>314</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>141</v>
+        <v>76</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -9268,7 +9286,7 @@
         <v>314</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -9276,7 +9294,7 @@
         <v>314</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
@@ -9284,7 +9302,7 @@
         <v>314</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
@@ -9292,7 +9310,7 @@
         <v>314</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -9300,7 +9318,7 @@
         <v>314</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -9308,7 +9326,7 @@
         <v>314</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
@@ -9316,7 +9334,7 @@
         <v>314</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
@@ -9324,7 +9342,7 @@
         <v>314</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -9332,7 +9350,7 @@
         <v>314</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -9340,7 +9358,7 @@
         <v>314</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -9348,7 +9366,7 @@
         <v>314</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -9356,7 +9374,7 @@
         <v>314</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -9364,7 +9382,7 @@
         <v>314</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -9372,7 +9390,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -9380,7 +9398,7 @@
         <v>314</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -9388,7 +9406,7 @@
         <v>314</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -9396,7 +9414,7 @@
         <v>314</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -9404,7 +9422,7 @@
         <v>314</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -9412,31 +9430,31 @@
         <v>314</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>314</v>
+        <v>250</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>60</v>
+        <v>251</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>118</v>
+        <v>253</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>157</v>
+        <v>314</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
@@ -9444,7 +9462,7 @@
         <v>315</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>161</v>
+        <v>60</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
@@ -9452,7 +9470,7 @@
         <v>315</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
@@ -9460,7 +9478,7 @@
         <v>315</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -9468,7 +9486,7 @@
         <v>315</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>195</v>
+        <v>161</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -9476,7 +9494,7 @@
         <v>315</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>221</v>
+        <v>168</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -9484,7 +9502,7 @@
         <v>315</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>224</v>
+        <v>175</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -9492,31 +9510,31 @@
         <v>315</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>315</v>
+        <v>195</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>77</v>
+        <v>221</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>85</v>
+        <v>224</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>93</v>
+        <v>315</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -9524,7 +9542,7 @@
         <v>316</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>148</v>
+        <v>77</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -9532,7 +9550,7 @@
         <v>316</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>154</v>
+        <v>85</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -9540,7 +9558,7 @@
         <v>316</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>155</v>
+        <v>93</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -9548,7 +9566,7 @@
         <v>316</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -9556,7 +9574,7 @@
         <v>316</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -9564,7 +9582,7 @@
         <v>316</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>206</v>
+        <v>155</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -9572,7 +9590,7 @@
         <v>316</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>208</v>
+        <v>156</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -9580,7 +9598,7 @@
         <v>316</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -9588,7 +9606,7 @@
         <v>316</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -9596,7 +9614,7 @@
         <v>316</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -9604,7 +9622,7 @@
         <v>316</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -9612,7 +9630,7 @@
         <v>316</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>302</v>
+        <v>217</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -9620,31 +9638,31 @@
         <v>316</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>316</v>
+        <v>226</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>66</v>
+        <v>244</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>158</v>
+        <v>302</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>162</v>
+        <v>316</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -9652,7 +9670,7 @@
         <v>318</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>219</v>
+        <v>66</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -9660,7 +9678,7 @@
         <v>318</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>246</v>
+        <v>158</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -9668,7 +9686,7 @@
         <v>318</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>318</v>
+        <v>162</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -9676,13 +9694,37 @@
         <v>318</v>
       </c>
       <c r="B299" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A300" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A301" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A302" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B302" s="2" t="s">
         <v>319</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B299" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B299">
-    <sortCondition ref="A2:A299"/>
+  <autoFilter ref="A1:B302" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B302">
+    <sortCondition ref="A2:A302"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/uorgs.xlsx
+++ b/uorgs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F00C01C-CFE8-40A2-A424-A20E410ADF94}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ED48FD7-A997-4399-9B2B-E15C5717E8C8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{EA73E3BE-6EDE-450B-BDC6-32103B9FB15B}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de UORGs e Departamen (2)'!$A$2:$E$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$302</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$303</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="339">
   <si>
     <t>ACP-SAR</t>
   </si>
@@ -1052,6 +1052,9 @@
   </si>
   <si>
     <t>CGRV</t>
+  </si>
+  <si>
+    <t>CNAS</t>
   </si>
 </sst>
 </file>
@@ -1576,10 +1579,10 @@
     <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1976,11 +1979,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
@@ -7243,7 +7246,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}">
-  <dimension ref="A1:E302"/>
+  <dimension ref="A1:E303"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.26953125" customWidth="1"/>
@@ -8669,7 +8672,7 @@
       <c r="A171" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B171" s="6" t="s">
+      <c r="B171" s="5" t="s">
         <v>335</v>
       </c>
     </row>
@@ -8677,7 +8680,7 @@
       <c r="A172" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B172" s="6" t="s">
+      <c r="B172" s="5" t="s">
         <v>336</v>
       </c>
     </row>
@@ -8685,7 +8688,7 @@
       <c r="A173" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B173" s="6" t="s">
+      <c r="B173" s="5" t="s">
         <v>337</v>
       </c>
     </row>
@@ -8693,8 +8696,8 @@
       <c r="A174" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B174" s="2" t="s">
-        <v>62</v>
+      <c r="B174" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
@@ -8702,7 +8705,7 @@
         <v>310</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
@@ -8710,7 +8713,7 @@
         <v>310</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -8718,7 +8721,7 @@
         <v>310</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
@@ -8726,7 +8729,7 @@
         <v>310</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
@@ -8734,7 +8737,7 @@
         <v>310</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
@@ -8742,7 +8745,7 @@
         <v>310</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
@@ -8750,7 +8753,7 @@
         <v>310</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -8758,7 +8761,7 @@
         <v>310</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
@@ -8766,7 +8769,7 @@
         <v>310</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
@@ -8774,7 +8777,7 @@
         <v>310</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -8782,7 +8785,7 @@
         <v>310</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -8790,7 +8793,7 @@
         <v>310</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -8798,7 +8801,7 @@
         <v>310</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -8806,7 +8809,7 @@
         <v>310</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -8814,7 +8817,7 @@
         <v>310</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -8822,7 +8825,7 @@
         <v>310</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -8830,7 +8833,7 @@
         <v>310</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -8838,7 +8841,7 @@
         <v>310</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -8846,7 +8849,7 @@
         <v>310</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -8854,7 +8857,7 @@
         <v>310</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
@@ -8862,7 +8865,7 @@
         <v>310</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -8870,7 +8873,7 @@
         <v>310</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -8878,7 +8881,7 @@
         <v>310</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -8886,7 +8889,7 @@
         <v>310</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -8894,7 +8897,7 @@
         <v>310</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -8902,7 +8905,7 @@
         <v>310</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>279</v>
+        <v>236</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -8910,7 +8913,7 @@
         <v>310</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
@@ -8918,7 +8921,7 @@
         <v>310</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
@@ -8926,7 +8929,7 @@
         <v>310</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
@@ -8934,15 +8937,15 @@
         <v>310</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>29</v>
+        <v>320</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
@@ -8950,7 +8953,7 @@
         <v>313</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
@@ -8958,7 +8961,7 @@
         <v>313</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
@@ -8966,7 +8969,7 @@
         <v>313</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
@@ -8974,7 +8977,7 @@
         <v>313</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
@@ -8982,7 +8985,7 @@
         <v>313</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
@@ -8990,7 +8993,7 @@
         <v>313</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -8998,7 +9001,7 @@
         <v>313</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
@@ -9006,7 +9009,7 @@
         <v>313</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
@@ -9022,7 +9025,7 @@
         <v>313</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
@@ -9038,7 +9041,7 @@
         <v>313</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -9046,7 +9049,7 @@
         <v>313</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -9054,7 +9057,7 @@
         <v>313</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
@@ -9062,7 +9065,7 @@
         <v>313</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -9070,7 +9073,7 @@
         <v>313</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -9078,7 +9081,7 @@
         <v>313</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
@@ -9086,7 +9089,7 @@
         <v>313</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
@@ -9094,7 +9097,7 @@
         <v>313</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -9102,7 +9105,7 @@
         <v>313</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
@@ -9110,7 +9113,7 @@
         <v>313</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
@@ -9118,7 +9121,7 @@
         <v>313</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
@@ -9126,7 +9129,7 @@
         <v>313</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -9134,7 +9137,7 @@
         <v>313</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
@@ -9142,7 +9145,7 @@
         <v>313</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -9150,7 +9153,7 @@
         <v>313</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
@@ -9158,7 +9161,7 @@
         <v>313</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -9166,7 +9169,7 @@
         <v>313</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
@@ -9174,7 +9177,7 @@
         <v>313</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -9182,7 +9185,7 @@
         <v>313</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -9190,7 +9193,7 @@
         <v>313</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -9198,7 +9201,7 @@
         <v>313</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -9206,7 +9209,7 @@
         <v>313</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -9214,7 +9217,7 @@
         <v>313</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -9222,7 +9225,7 @@
         <v>313</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>303</v>
+        <v>241</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -9230,15 +9233,15 @@
         <v>313</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>21</v>
+        <v>313</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
@@ -9246,7 +9249,7 @@
         <v>314</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
@@ -9254,7 +9257,7 @@
         <v>314</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
@@ -9262,7 +9265,7 @@
         <v>314</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
@@ -9270,7 +9273,7 @@
         <v>314</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
@@ -9278,7 +9281,7 @@
         <v>314</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -9286,7 +9289,7 @@
         <v>314</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
@@ -9294,7 +9297,7 @@
         <v>314</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
@@ -9302,7 +9305,7 @@
         <v>314</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
@@ -9310,7 +9313,7 @@
         <v>314</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -9318,7 +9321,7 @@
         <v>314</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -9326,7 +9329,7 @@
         <v>314</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
@@ -9334,7 +9337,7 @@
         <v>314</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
@@ -9342,7 +9345,7 @@
         <v>314</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -9350,7 +9353,7 @@
         <v>314</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -9358,7 +9361,7 @@
         <v>314</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -9366,7 +9369,7 @@
         <v>314</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -9374,7 +9377,7 @@
         <v>314</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -9382,7 +9385,7 @@
         <v>314</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -9390,7 +9393,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -9398,7 +9401,7 @@
         <v>314</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -9406,7 +9409,7 @@
         <v>314</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -9414,7 +9417,7 @@
         <v>314</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -9422,7 +9425,7 @@
         <v>314</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -9430,7 +9433,7 @@
         <v>314</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
@@ -9438,7 +9441,7 @@
         <v>314</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -9446,7 +9449,7 @@
         <v>314</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -9454,15 +9457,15 @@
         <v>314</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>314</v>
+        <v>253</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>60</v>
+        <v>314</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
@@ -9470,7 +9473,7 @@
         <v>315</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
@@ -9478,7 +9481,7 @@
         <v>315</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
@@ -9486,7 +9489,7 @@
         <v>315</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
@@ -9494,7 +9497,7 @@
         <v>315</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
@@ -9502,7 +9505,7 @@
         <v>315</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
@@ -9510,7 +9513,7 @@
         <v>315</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
@@ -9518,7 +9521,7 @@
         <v>315</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -9526,7 +9529,7 @@
         <v>315</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -9534,15 +9537,15 @@
         <v>315</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>315</v>
+        <v>224</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>77</v>
+        <v>315</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
@@ -9550,7 +9553,7 @@
         <v>316</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
@@ -9558,7 +9561,7 @@
         <v>316</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
@@ -9566,7 +9569,7 @@
         <v>316</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>148</v>
+        <v>93</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
@@ -9574,7 +9577,7 @@
         <v>316</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
@@ -9582,7 +9585,7 @@
         <v>316</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
@@ -9590,7 +9593,7 @@
         <v>316</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
@@ -9598,7 +9601,7 @@
         <v>316</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -9606,7 +9609,7 @@
         <v>316</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -9614,7 +9617,7 @@
         <v>316</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -9622,7 +9625,7 @@
         <v>316</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -9630,7 +9633,7 @@
         <v>316</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -9638,7 +9641,7 @@
         <v>316</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -9646,7 +9649,7 @@
         <v>316</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -9654,7 +9657,7 @@
         <v>316</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>302</v>
+        <v>244</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -9662,15 +9665,15 @@
         <v>316</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>66</v>
+        <v>316</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
@@ -9678,7 +9681,7 @@
         <v>318</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>158</v>
+        <v>66</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
@@ -9686,7 +9689,7 @@
         <v>318</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
@@ -9694,7 +9697,7 @@
         <v>318</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
@@ -9702,7 +9705,7 @@
         <v>318</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
@@ -9710,7 +9713,7 @@
         <v>318</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>318</v>
+        <v>246</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
@@ -9718,13 +9721,21 @@
         <v>318</v>
       </c>
       <c r="B302" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A303" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B303" s="2" t="s">
         <v>319</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B302" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B302">
-    <sortCondition ref="A2:A302"/>
+  <autoFilter ref="A1:B303" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B303">
+    <sortCondition ref="A2:A303"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/uorgs.xlsx
+++ b/uorgs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ED48FD7-A997-4399-9B2B-E15C5717E8C8}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{AC2FE9AA-3F07-4D79-BF1E-996DB9CB6A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4132B0D-F834-4B1F-8FCA-115C90A3D196}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{EA73E3BE-6EDE-450B-BDC6-32103B9FB15B}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lista de UORGs e Departamen (2)'!$A$2:$E$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$303</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">UORGs!$A$1:$B$310</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1532" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="345">
   <si>
     <t>ACP-SAR</t>
   </si>
@@ -1055,6 +1055,24 @@
   </si>
   <si>
     <t>CNAS</t>
+  </si>
+  <si>
+    <t>COAG-CWB</t>
+  </si>
+  <si>
+    <t>COAG-POA</t>
+  </si>
+  <si>
+    <t>COAG-SSA</t>
+  </si>
+  <si>
+    <t>GTCG</t>
+  </si>
+  <si>
+    <t>GTFA</t>
+  </si>
+  <si>
+    <t>COAG-REC</t>
   </si>
 </sst>
 </file>
@@ -7246,7 +7264,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}">
-  <dimension ref="A1:E303"/>
+  <dimension ref="A1:E310"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.26953125" customWidth="1"/>
@@ -7936,48 +7954,48 @@
       <c r="A79" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>2</v>
+      <c r="B79" s="1" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>104</v>
+      <c r="B80" s="1" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>159</v>
+      <c r="B81" s="1" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>167</v>
+      <c r="B82" s="1" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>183</v>
+      <c r="B83" s="1" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>214</v>
+      <c r="B84" s="1" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
@@ -7985,7 +8003,7 @@
         <v>326</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>215</v>
+        <v>326</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
@@ -7993,7 +8011,7 @@
         <v>326</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>234</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
@@ -8001,7 +8019,7 @@
         <v>326</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>255</v>
+        <v>104</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
@@ -8009,7 +8027,7 @@
         <v>326</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>256</v>
+        <v>159</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -8017,7 +8035,7 @@
         <v>326</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>257</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
@@ -8025,7 +8043,7 @@
         <v>326</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>258</v>
+        <v>183</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
@@ -8033,7 +8051,7 @@
         <v>326</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>259</v>
+        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
@@ -8041,7 +8059,7 @@
         <v>326</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>260</v>
+        <v>215</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
@@ -8049,7 +8067,7 @@
         <v>326</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
@@ -8057,7 +8075,7 @@
         <v>326</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
@@ -8065,7 +8083,7 @@
         <v>326</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
@@ -8073,7 +8091,7 @@
         <v>326</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
@@ -8081,7 +8099,7 @@
         <v>326</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
@@ -8089,7 +8107,7 @@
         <v>326</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
@@ -8097,7 +8115,7 @@
         <v>326</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
@@ -8105,7 +8123,7 @@
         <v>326</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
@@ -8113,7 +8131,7 @@
         <v>326</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
@@ -8121,7 +8139,7 @@
         <v>326</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
@@ -8129,7 +8147,7 @@
         <v>326</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -8137,7 +8155,7 @@
         <v>326</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
@@ -8145,7 +8163,7 @@
         <v>326</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
@@ -8153,7 +8171,7 @@
         <v>326</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
@@ -8161,7 +8179,7 @@
         <v>326</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -8169,7 +8187,7 @@
         <v>326</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
@@ -8177,7 +8195,7 @@
         <v>326</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
@@ -8185,7 +8203,7 @@
         <v>326</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
@@ -8193,7 +8211,7 @@
         <v>326</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
@@ -8201,63 +8219,63 @@
         <v>326</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>307</v>
+        <v>273</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>0</v>
+        <v>274</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>9</v>
+        <v>275</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>151</v>
+        <v>276</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>179</v>
+        <v>277</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>185</v>
+        <v>278</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>186</v>
+        <v>284</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
-        <v>301</v>
+        <v>326</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>187</v>
+        <v>307</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
@@ -8265,7 +8283,7 @@
         <v>301</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
@@ -8273,7 +8291,7 @@
         <v>301</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>209</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
@@ -8281,7 +8299,7 @@
         <v>301</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>211</v>
+        <v>151</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -8289,7 +8307,7 @@
         <v>301</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>227</v>
+        <v>179</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -8297,7 +8315,7 @@
         <v>301</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>237</v>
+        <v>185</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -8305,7 +8323,7 @@
         <v>301</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>238</v>
+        <v>186</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -8313,7 +8331,7 @@
         <v>301</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>240</v>
+        <v>187</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
@@ -8321,7 +8339,7 @@
         <v>301</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>243</v>
+        <v>202</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -8329,7 +8347,7 @@
         <v>301</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>248</v>
+        <v>209</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -8337,7 +8355,7 @@
         <v>301</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>249</v>
+        <v>211</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -8345,7 +8363,7 @@
         <v>301</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
@@ -8353,63 +8371,63 @@
         <v>301</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>301</v>
+        <v>237</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>170</v>
+        <v>238</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>289</v>
+        <v>252</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
@@ -8417,7 +8435,7 @@
         <v>308</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>298</v>
+        <v>170</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
@@ -8425,63 +8443,63 @@
         <v>308</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>308</v>
+        <v>178</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>4</v>
+        <v>190</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>31</v>
+        <v>242</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>32</v>
+        <v>247</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>38</v>
+        <v>289</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>39</v>
+        <v>290</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>41</v>
+        <v>298</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>43</v>
+        <v>308</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
@@ -8489,7 +8507,7 @@
         <v>309</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
@@ -8497,7 +8515,7 @@
         <v>309</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
@@ -8505,7 +8523,7 @@
         <v>309</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
@@ -8513,7 +8531,7 @@
         <v>309</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -8521,7 +8539,7 @@
         <v>309</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>90</v>
+        <v>39</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
@@ -8529,7 +8547,7 @@
         <v>309</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -8537,7 +8555,7 @@
         <v>309</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
@@ -8545,7 +8563,7 @@
         <v>309</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
@@ -8553,7 +8571,7 @@
         <v>309</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
@@ -8561,7 +8579,7 @@
         <v>309</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
@@ -8569,7 +8587,7 @@
         <v>309</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
@@ -8577,7 +8595,7 @@
         <v>309</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
@@ -8585,7 +8603,7 @@
         <v>309</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>133</v>
+        <v>91</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
@@ -8593,7 +8611,7 @@
         <v>309</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>145</v>
+        <v>94</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -8601,7 +8619,7 @@
         <v>309</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
@@ -8609,7 +8627,7 @@
         <v>309</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>153</v>
+        <v>101</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -8617,7 +8635,7 @@
         <v>309</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>163</v>
+        <v>103</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
@@ -8625,7 +8643,7 @@
         <v>309</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>191</v>
+        <v>105</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -8633,7 +8651,7 @@
         <v>309</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>196</v>
+        <v>116</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
@@ -8641,7 +8659,7 @@
         <v>309</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>254</v>
+        <v>133</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
@@ -8649,7 +8667,7 @@
         <v>309</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>299</v>
+        <v>145</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
@@ -8657,63 +8675,63 @@
         <v>309</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>309</v>
+        <v>150</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>33</v>
+        <v>153</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B171" s="5" t="s">
-        <v>335</v>
+        <v>309</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B172" s="5" t="s">
-        <v>336</v>
+        <v>309</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B173" s="5" t="s">
-        <v>337</v>
+        <v>309</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B174" s="5" t="s">
-        <v>338</v>
+        <v>309</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>62</v>
+        <v>299</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>86</v>
+        <v>309</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -8721,39 +8739,39 @@
         <v>310</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>92</v>
+      <c r="B178" s="5" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>102</v>
+      <c r="B179" s="5" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B180" s="2" t="s">
-        <v>109</v>
+      <c r="B180" s="5" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>115</v>
+      <c r="B181" s="5" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
@@ -8761,7 +8779,7 @@
         <v>310</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>119</v>
+        <v>62</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
@@ -8769,7 +8787,7 @@
         <v>310</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
@@ -8777,7 +8795,7 @@
         <v>310</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>129</v>
+        <v>87</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
@@ -8785,7 +8803,7 @@
         <v>310</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -8793,7 +8811,7 @@
         <v>310</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
@@ -8801,7 +8819,7 @@
         <v>310</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
@@ -8809,7 +8827,7 @@
         <v>310</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
@@ -8817,7 +8835,7 @@
         <v>310</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>172</v>
+        <v>119</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
@@ -8825,7 +8843,7 @@
         <v>310</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
@@ -8833,7 +8851,7 @@
         <v>310</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>192</v>
+        <v>129</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
@@ -8841,7 +8859,7 @@
         <v>310</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>200</v>
+        <v>136</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
@@ -8849,7 +8867,7 @@
         <v>310</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>205</v>
+        <v>140</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
@@ -8857,7 +8875,7 @@
         <v>310</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>207</v>
+        <v>149</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
@@ -8865,7 +8883,7 @@
         <v>310</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>213</v>
+        <v>165</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
@@ -8873,7 +8891,7 @@
         <v>310</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>216</v>
+        <v>172</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
@@ -8881,7 +8899,7 @@
         <v>310</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>218</v>
+        <v>177</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
@@ -8889,7 +8907,7 @@
         <v>310</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
@@ -8897,7 +8915,7 @@
         <v>310</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
@@ -8905,7 +8923,7 @@
         <v>310</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
@@ -8913,7 +8931,7 @@
         <v>310</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>279</v>
+        <v>207</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
@@ -8921,7 +8939,7 @@
         <v>310</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>287</v>
+        <v>213</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
@@ -8929,7 +8947,7 @@
         <v>310</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>288</v>
+        <v>216</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
@@ -8937,7 +8955,7 @@
         <v>310</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>310</v>
+        <v>218</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
@@ -8945,63 +8963,63 @@
         <v>310</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>320</v>
+        <v>229</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>29</v>
+        <v>233</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>37</v>
+        <v>236</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>40</v>
+        <v>279</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>42</v>
+        <v>287</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>45</v>
+        <v>288</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>46</v>
+        <v>310</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>47</v>
+        <v>320</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
@@ -9009,7 +9027,7 @@
         <v>313</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
@@ -9017,7 +9035,7 @@
         <v>313</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
@@ -9025,7 +9043,7 @@
         <v>313</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
@@ -9033,7 +9051,7 @@
         <v>313</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
@@ -9041,7 +9059,7 @@
         <v>313</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
@@ -9049,7 +9067,7 @@
         <v>313</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
@@ -9057,7 +9075,7 @@
         <v>313</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
@@ -9065,7 +9083,7 @@
         <v>313</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
@@ -9073,7 +9091,7 @@
         <v>313</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
@@ -9081,7 +9099,7 @@
         <v>313</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
@@ -9089,7 +9107,7 @@
         <v>313</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
@@ -9097,7 +9115,7 @@
         <v>313</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
@@ -9105,7 +9123,7 @@
         <v>313</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
@@ -9113,7 +9131,7 @@
         <v>313</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
@@ -9121,7 +9139,7 @@
         <v>313</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
@@ -9129,7 +9147,7 @@
         <v>313</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
@@ -9137,7 +9155,7 @@
         <v>313</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
@@ -9145,7 +9163,7 @@
         <v>313</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
@@ -9153,7 +9171,7 @@
         <v>313</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
@@ -9161,7 +9179,7 @@
         <v>313</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
@@ -9169,7 +9187,7 @@
         <v>313</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
@@ -9177,7 +9195,7 @@
         <v>313</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>160</v>
+        <v>84</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
@@ -9185,7 +9203,7 @@
         <v>313</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
@@ -9193,7 +9211,7 @@
         <v>313</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>176</v>
+        <v>97</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
@@ -9201,7 +9219,7 @@
         <v>313</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>193</v>
+        <v>120</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
@@ -9209,7 +9227,7 @@
         <v>313</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>201</v>
+        <v>128</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -9217,7 +9235,7 @@
         <v>313</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>230</v>
+        <v>131</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
@@ -9225,7 +9243,7 @@
         <v>313</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>241</v>
+        <v>137</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
@@ -9233,7 +9251,7 @@
         <v>313</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>303</v>
+        <v>160</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
@@ -9241,63 +9259,63 @@
         <v>313</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>313</v>
+        <v>166</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>21</v>
+        <v>176</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>50</v>
+        <v>201</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>54</v>
+        <v>230</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>71</v>
+        <v>241</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>76</v>
+        <v>303</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>111</v>
+        <v>313</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
@@ -9305,7 +9323,7 @@
         <v>314</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>130</v>
+        <v>21</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
@@ -9313,7 +9331,7 @@
         <v>314</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>141</v>
+        <v>44</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -9321,7 +9339,7 @@
         <v>314</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
@@ -9329,7 +9347,7 @@
         <v>314</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>146</v>
+        <v>54</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
@@ -9337,7 +9355,7 @@
         <v>314</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>147</v>
+        <v>71</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
@@ -9345,7 +9363,7 @@
         <v>314</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>152</v>
+        <v>76</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
@@ -9353,7 +9371,7 @@
         <v>314</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>173</v>
+        <v>111</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
@@ -9361,7 +9379,7 @@
         <v>314</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
@@ -9369,7 +9387,7 @@
         <v>314</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
@@ -9377,7 +9395,7 @@
         <v>314</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
@@ -9385,7 +9403,7 @@
         <v>314</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>194</v>
+        <v>146</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
@@ -9393,7 +9411,7 @@
         <v>314</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>197</v>
+        <v>147</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
@@ -9401,7 +9419,7 @@
         <v>314</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
@@ -9409,7 +9427,7 @@
         <v>314</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
@@ -9417,7 +9435,7 @@
         <v>314</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
@@ -9425,7 +9443,7 @@
         <v>314</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
@@ -9433,7 +9451,7 @@
         <v>314</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>232</v>
+        <v>184</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
@@ -9441,7 +9459,7 @@
         <v>314</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>250</v>
+        <v>194</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
@@ -9449,7 +9467,7 @@
         <v>314</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>251</v>
+        <v>197</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
@@ -9457,7 +9475,7 @@
         <v>314</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>253</v>
+        <v>198</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
@@ -9465,63 +9483,63 @@
         <v>314</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>314</v>
+        <v>199</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>60</v>
+        <v>228</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>118</v>
+        <v>231</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>157</v>
+        <v>232</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>161</v>
+        <v>250</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>168</v>
+        <v>251</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>175</v>
+        <v>253</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>195</v>
+        <v>314</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
@@ -9529,7 +9547,7 @@
         <v>315</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>221</v>
+        <v>60</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -9537,7 +9555,7 @@
         <v>315</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>224</v>
+        <v>118</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
@@ -9545,63 +9563,63 @@
         <v>315</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>315</v>
+        <v>157</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>77</v>
+        <v>161</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>85</v>
+        <v>168</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>154</v>
+        <v>221</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>155</v>
+        <v>224</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>156</v>
+        <v>315</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
@@ -9609,7 +9627,7 @@
         <v>316</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
@@ -9617,7 +9635,7 @@
         <v>316</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>206</v>
+        <v>85</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
@@ -9625,7 +9643,7 @@
         <v>316</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>208</v>
+        <v>93</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
@@ -9633,7 +9651,7 @@
         <v>316</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>210</v>
+        <v>148</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
@@ -9641,7 +9659,7 @@
         <v>316</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>217</v>
+        <v>154</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
@@ -9649,7 +9667,7 @@
         <v>316</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>226</v>
+        <v>155</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
@@ -9657,7 +9675,7 @@
         <v>316</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>244</v>
+        <v>156</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
@@ -9665,7 +9683,7 @@
         <v>316</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>302</v>
+        <v>189</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
@@ -9673,69 +9691,125 @@
         <v>316</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>316</v>
+        <v>206</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>66</v>
+        <v>208</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>158</v>
+        <v>210</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>162</v>
+        <v>217</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A304" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="B303" s="2" t="s">
+      <c r="B304" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A305" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A306" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A307" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A308" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A309" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A310" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B310" s="2" t="s">
         <v>319</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B303" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B303">
-    <sortCondition ref="A2:A303"/>
+  <autoFilter ref="A1:B310" xr:uid="{EBAED548-1DB8-42E0-935D-EA8DEC6A284E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B310">
+    <sortCondition ref="A2:A310"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
